--- a/output/Table_B_Expansion.xlsx
+++ b/output/Table_B_Expansion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,21 +458,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1341ka</t>
+          <t>0101ka</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>verbal reciprocal/reflexive &gt; verb agreement with subject</t>
+          <t>N-Gen &gt; N-Adj</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>If a language has a verbal reciprocal/reflexive, it must have an overt AGR marker. Standardized IF there is a verbal reciprocal/reflexive, THEN there must be verb agreement at least with subject.</t>
+          <t>If the possessive adjective follows the noun, then the descriptive adjective follows the noun.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.06860198256716</v>
+        <v>1.263458887313696</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -483,21 +483,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0917bka</t>
+          <t>1341ka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OV &gt; Gen-N</t>
+          <t>verbal reciprocal/reflexive &gt; verb agreement with subject</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consistent OV languages are consistently left-branching (placing phrasal constituents before nonphrasal ones) while consistent VO languages are consistently right-branching.</t>
+          <t>If a language has a verbal reciprocal/reflexive, it must have an overt AGR marker. Standardized IF there is a verbal reciprocal/reflexive, THEN there must be verb agreement at least with subject.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.87495728233763</v>
+        <v>1.123052788661962</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -508,21 +508,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0001_or_2bka</t>
+          <t>0917bka</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N-Adp &gt; Gen-N</t>
+          <t>OV &gt; Gen-N</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Universal 2. In languages with prepositions, the genitive almost always follows the governing noun, while in languages with postpositions it almost always precedes</t>
+          <t>Consistent OV languages are consistently left-branching (placing phrasal constituents before nonphrasal ones) while consistent VO languages are consistently right-branching.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.17245643175537</v>
+        <v>1.872708679895618</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -533,21 +533,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0101ka</t>
+          <t>0001_or_2bka</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N-Gen &gt; N-Adj</t>
+          <t>N-Adp &gt; Gen-N</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>If the possessive adjective follows the noun, then the descriptive adjective follows the noun.</t>
+          <t>Universal 2. In languages with prepositions, the genitive almost always follows the governing noun, while in languages with postpositions it almost always precedes</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.04932850833503</v>
+        <v>1.214776970483311</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -558,21 +558,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0062bka</t>
+          <t>1591ka</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rel-N &gt; N-Adp</t>
+          <t>internal relative clause &gt; SOV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Universal 24. If the relative expression precedes the noun either as the only construction or as an alternate construction, either the language is postpositional, or the adjective precedes the noun or both.</t>
+          <t>Clear cases of internal relative clauses are present only in languages whose basic word order is SOV.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.34308162248338</v>
+        <v>1.177530501362346</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -583,21 +583,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0511aka</t>
+          <t>0062bka</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Trial &gt; Dual</t>
+          <t>Rel-N &gt; N-Adp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Universal 34. No language has a trial number unless it has a dual. No language has a dual unless it has a plural.</t>
+          <t>Universal 24. If the relative expression precedes the noun either as the only construction or as an alternate construction, either the language is postpositional, or the adjective precedes the noun or both.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.805706481607549</v>
+        <v>1.318367109669455</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.46294622771938</v>
+        <v>1.400039618483887</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.64905779249504</v>
+        <v>1.46868768103183</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.656080415809852</v>
+        <v>0.6648923245892728</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -683,21 +683,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1591ka</t>
+          <t>0582ka</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>internal relative clause &gt; SOV</t>
+          <t>inflection (noun) &gt; inflection (pronoun)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Clear cases of internal relative clauses are present only in languages whose basic word order is SOV.</t>
+          <t>If there is any inflection in nouns, there are also some inflections in pronouns.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.21373601831811</v>
+        <v>0.6197475983185543</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -708,21 +708,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0582ka</t>
+          <t>1667aka</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>inflection (noun) &gt; inflection (pronoun)</t>
+          <t>S-Comp &gt; SOV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>If there is any inflection in nouns, there are also some inflections in pronouns.</t>
+          <t>There is a tendency for conjunctions (including comlementizers) to occur in clause-final position in SOV languages and in clause-initial position in VSO languages.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.615850581387366</v>
+        <v>1.343421666206671</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -733,21 +733,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1667aka</t>
+          <t>0091ka</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S-Comp &gt; SOV</t>
+          <t>Adp-N &amp; N-Adj &gt; N-Rel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>There is a tendency for conjunctions (including comlementizers) to occur in clause-final position in SOV languages and in clause-initial position in VSO languages.</t>
+          <t>IF a language has Prep word order, then if the adjective follows the noun, the relative clause follows the noun.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.25280100958432</v>
+        <v>1.812095823486219</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -758,21 +758,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0091ka</t>
+          <t>1427ka</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Adj &gt; N-Rel</t>
+          <t>no prefix &gt; infl local cases</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IF a language has Prep word order, then if the adjective follows the noun, the relative clause follows the noun.</t>
+          <t>If in a language there are no prefixes, then there will be inflectional (i.e. not prepositional) local cases.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.89409686268089</v>
+        <v>-0.9684874402709036</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0178ka</t>
+          <t>1994dka</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N-Adp &amp; Num-N &gt; Gen-N</t>
+          <t>non-affixed Gen-N &gt; Adj-N</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>If a language has Postp word order, then if the numeral precedes the noun, the genitive precedes the noun.</t>
+          <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.08765000355159</v>
+        <v>1.194464966759849</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1827ka</t>
+          <t>0178ka</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rel-N | Adj-N &gt; Gen-N</t>
+          <t>N-Adp &amp; Num-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>If a language shows the order RelNoun or AdjNoun in its noun phrase, it is very likely to also show PossNoun, but not vice versa.</t>
+          <t>If a language has Postp word order, then if the numeral precedes the noun, the genitive precedes the noun.</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.86596368328413</v>
+        <v>1.110359375235017</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.950094905567595</v>
+        <v>0.8919097611188793</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -858,21 +858,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0493bka</t>
+          <t>0071ka</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sent-Q &gt; N-Adp</t>
+          <t>N-Adp &amp; Adj-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Universal 9. With well more than chance frequency, when question particles or affixes are specified in position by reference to the sentence as a whole, if initial, such elements are found in prepositional languages, and, if final, in postpositional.</t>
+          <t>If a language has Postp word order, and if the adjective precedes the noun, then the genitive precedes the noun.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.708040573280932</v>
+        <v>1.479624613181985</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -883,21 +883,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0071ka</t>
+          <t>0493bka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N-Adp &amp; Adj-N &gt; Gen-N</t>
+          <t>Sent-Q &gt; N-Adp</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>If a language has Postp word order, and if the adjective precedes the noun, then the genitive precedes the noun.</t>
+          <t>Universal 9. With well more than chance frequency, when question particles or affixes are specified in position by reference to the sentence as a whole, if initial, such elements are found in prepositional languages, and, if final, in postpositional.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.55905719145889</v>
+        <v>0.6554210903288318</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1994dka</t>
+          <t>1827ka</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>non-affixed Gen-N &gt; Adj-N</t>
+          <t>Rel-N | Adj-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
+          <t>If a language shows the order RelNoun or AdjNoun in its noun phrase, it is very likely to also show PossNoun, but not vice versa.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.10452437572336</v>
+        <v>0.8487445702647829</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0982ka</t>
+          <t>0110ka</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>locative comparative &gt; SOV | VSO</t>
+          <t>N-Rel &gt; N-Adj</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>If a language has a locative comparative, then it is either SOV or VSO.</t>
+          <t>There is a clear tendency for Rel N languages to be Adj N and for N Rel languages to be N Adj.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.773816123753111</v>
+        <v>0.8680778033647435</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -958,21 +958,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0110ka</t>
+          <t>1267aka</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>N-Rel &gt; N-Adj</t>
+          <t>ergative &gt; VSO | SOV</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>There is a clear tendency for Rel N languages to be Adj N and for N Rel languages to be N Adj.</t>
+          <t>Ergative systems are found only in SOV and VSO languages. SVO languages are never ergative.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.875516085380692</v>
+        <v>1.14618148201946</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -983,21 +983,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0983ka</t>
+          <t>0982ka</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>exceed comparative &gt; SVO</t>
+          <t>locative comparative &gt; SOV | VSO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>If a language has an exceed comparative, then it is SVO.</t>
+          <t>If a language has a locative comparative, then it is either SOV or VSO.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.839916644806777</v>
+        <v>0.7824118196564633</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1008,21 +1008,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1267aka</t>
+          <t>0983ka</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ergative &gt; VSO | SOV</t>
+          <t>exceed comparative &gt; SVO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ergative systems are found only in SOV and VSO languages. SVO languages are never ergative.</t>
+          <t>If a language has an exceed comparative, then it is SVO.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.16239035270345</v>
+        <v>0.8002579058598616</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0507ka</t>
+          <t>0493aka</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>(person)-number (verb) &gt; tense-mood (verb)</t>
+          <t>Q-Sent &gt; Adp-N</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>If the verb has categories of person-number or if it has categories of gender, it always has tense-mood categories.</t>
+          <t>Universal 9. With well more than chance frequency, when question particles or affixes are specified in position by reference to the sentence as a whole, if initial, such elements are found in prepositional languages, and, if final, in postpositional.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.845668994377661</v>
+        <v>0.8773918990590241</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1058,21 +1058,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1612cka</t>
+          <t>1431nka</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOV &amp; N-Num &gt; N-Num agr</t>
+          <t>more case &gt; less tense</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>In SOV languages, when the expected order of Modifier-Noun does not occur,  agreement [between noun and modifier] tends to appear.</t>
+          <t>The more developed a case system is, the less is its system of verbal tenses.</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-7.36159513784198</v>
+        <v>-0.7330741943451813</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0493aka</t>
+          <t>0507ka</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q-Sent &gt; Adp-N</t>
+          <t>(person)-number (verb) &gt; tense-mood (verb)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Universal 9. With well more than chance frequency, when question particles or affixes are specified in position by reference to the sentence as a whole, if initial, such elements are found in prepositional languages, and, if final, in postpositional.</t>
+          <t>If the verb has categories of person-number or if it has categories of gender, it always has tense-mood categories.</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.909071086015209</v>
+        <v>0.9402568206468179</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.31375821178423</v>
+        <v>1.267659628830224</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0245aka</t>
+          <t>0147ka</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>free order &gt; inflection nouns</t>
+          <t>V-like Attr Adj &gt; SVO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>If constituent order is free without limits, then nominal words are inflected, but not vice versa; if constituent order is rigid without inversions, then there is no nominal inflection, but again not vice versa.</t>
+          <t>If attributive adjectives have the form of relative clauses, there is a positive correlation with SVO.</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.461229210016715</v>
+        <v>-0.5407045909718766</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1158,21 +1158,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1549ka</t>
+          <t>1612cka</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>V-initial &gt; N-Gen</t>
+          <t>SOV &amp; N-Num &gt; N-Num agr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>With great regularity possessor NPs follow the head NP in verb-initial languages.</t>
+          <t>In SOV languages, when the expected order of Modifier-Noun does not occur,  agreement [between noun and modifier] tends to appear.</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.873738289789306</v>
+        <v>-4.266092981394785</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1183,21 +1183,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0231bka</t>
+          <t>0008ka</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>free order | case &gt; gradation adj inflect</t>
+          <t>SOV|OSV &gt; case</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>If constituent order is rigid (or if there is no case inflection), then the gradation of adjectives is expressed by function words; if constituent order is flexible (or if there is case inflection), then the gradation of adjectives is expressed inflectionally.</t>
+          <t>Universal 41. If in a language the verb follows both the nominal subject and nominal object as the dominant order, the language almost always has a case system.</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.664393740917643</v>
+        <v>0.8683754606800662</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1208,21 +1208,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1431nka</t>
+          <t>0245aka</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>more case &gt; less tense</t>
+          <t>free order &gt; inflection nouns</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The more developed a case system is, the less is its system of verbal tenses.</t>
+          <t>If constituent order is free without limits, then nominal words are inflected, but not vice versa; if constituent order is rigid without inversions, then there is no nominal inflection, but again not vice versa.</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.6945574630192231</v>
+        <v>0.4236947200639888</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1233,21 +1233,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0228ka</t>
+          <t>0231bka</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nominal case &gt; verbal inflection</t>
+          <t>free order | case &gt; gradation adj inflect</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>If nouns inflect for case, then verbs inflect for some inflectional category.</t>
+          <t>If constituent order is rigid (or if there is no case inflection), then the gradation of adjectives is expressed by function words; if constituent order is flexible (or if there is case inflection), then the gradation of adjectives is expressed inflectionally.</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.05194415818154</v>
+        <v>0.7408322774174536</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1258,21 +1258,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1427ka</t>
+          <t>0964bka</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no prefix &gt; infl local cases</t>
+          <t>OV &gt; N-Art</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>If in a language there are no prefixes, then there will be inflectional (i.e. not prepositional) local cases.</t>
+          <t>VO languages exhibit a statistically greater tendency to place articles before the noun than OV languages do. To the opposite, the tendency to place the noun before the articles is higher among OV languages than it is among VO languages.</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.907106083712564</v>
+        <v>0.7995804208801867</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0964bka</t>
+          <t>1027bka</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OV &gt; N-Art</t>
+          <t>no morph tense -&gt; no case|VO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VO languages exhibit a statistically greater tendency to place articles before the noun than OV languages do. To the opposite, the tendency to place the noun before the articles is higher among OV languages than it is among VO languages.</t>
+          <t>There are correlations between following parameters: VO word order, Non-tensedness, Non-casedness, WITH-Construction, Non-Absolute Converb. Standardized IF VO, THEN Non-tensedness, Non-casedness, WITH-Construction, and Non-Absolute Converb. IF Non-tensedness, THEN VO, Non-casedness, WITH-Construction, and Non-Absolute Converb. IF Non-casedness, THEN VO, Non-tensedness, WITH-Construction, and Non-Absolute Converb. IF AND-construction, THEN VO, Non-tensedness, Non-casedness, and Non-Absolute Converb. IF Non-Absolute Converb, THEN VO, Non-tensedness, Non-casedness, and WITH-Construction.</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.780455522336843</v>
+        <v>0.6468513608332771</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0008ka</t>
+          <t>0070ka</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SOV|OSV &gt; case</t>
+          <t>Adp-N &amp; no SVO &amp; N-Adj &gt; N-Gen</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Universal 41. If in a language the verb follows both the nominal subject and nominal object as the dominant order, the language almost always has a case system.</t>
+          <t>If a language has prepositions and any verb position other than SVO, then if the adjectives follows the noun, the genitive follows the noun.</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.874220459085075</v>
+        <v>0.9936874289930697</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1550ka</t>
+          <t>1592ka</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>V-initial &gt; N-Rel</t>
+          <t>internal relative clause &gt; left-branching NP structure</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>In verb-initial languages the dominant order of relative clauses is always postnominal.</t>
+          <t>The restriction of internally headed relative clauses to OV languages implies that these relative clauses are found in languages having left-branching rather than (in addition to) right-branching NP structure.</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.31014372381212</v>
+        <v>0.6092661184715494</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0116ka</t>
+          <t>1434ka</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>case &gt; number</t>
+          <t>many tenses &gt; no aspect</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>number is, as has been seen, closer to the stem and generally present when case is present, while the opposite relation holds far more rarely.</t>
+          <t>A large number of tense oppositions correlates with the absence of aspect differentiation.</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.28165266187472</v>
+        <v>0.473181485800218</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1383,21 +1383,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1434ka</t>
+          <t>0116ka</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>many tenses &gt; no aspect</t>
+          <t>case &gt; number</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A large number of tense oppositions correlates with the absence of aspect differentiation.</t>
+          <t>number is, as has been seen, closer to the stem and generally present when case is present, while the opposite relation holds far more rarely.</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.466455356140432</v>
+        <v>0.3399723047312557</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1408,21 +1408,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1027bka</t>
+          <t>0822ka</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no morph tense -&gt; no case|VO</t>
+          <t>correlative Rel &gt; V-final;</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>There are correlations between following parameters: VO word order, Non-tensedness, Non-casedness, WITH-Construction, Non-Absolute Converb. Standardized IF VO, THEN Non-tensedness, Non-casedness, WITH-Construction, and Non-Absolute Converb. IF Non-tensedness, THEN VO, Non-casedness, WITH-Construction, and Non-Absolute Converb. IF Non-casedness, THEN VO, Non-tensedness, WITH-Construction, and Non-Absolute Converb. IF AND-construction, THEN VO, Non-tensedness, Non-casedness, and Non-Absolute Converb. IF Non-Absolute Converb, THEN VO, Non-tensedness, Non-casedness, and WITH-Construction.</t>
+          <t>Correlatives are limited to verb-final languages, and in fact, are largely limited to "loose" verb-final ones, namely which permit some NPs, especially "heavy" ones to occur to the right of the verb without any special effect of foregrounding or backgrounding.</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.8034289834384321</v>
+        <v>0.7531105468410542</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1216ka</t>
+          <t>0228ka</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N-Adp &gt; case (noun)</t>
+          <t>nominal case &gt; verbal inflection</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>If there are (local) postpositions, then there will also be nominal case inflection (not necessarily including local cases, though).</t>
+          <t>If nouns inflect for case, then verbs inflect for some inflectional category.</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.553925847341954</v>
+        <v>1.492674779222098</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0822ka</t>
+          <t>0798ka</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>correlative Rel &gt; V-final;</t>
+          <t>tensed &gt; N-like Pred Adj</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Correlatives are limited to verb-final languages, and in fact, are largely limited to "loose" verb-final ones, namely which permit some NPs, especially "heavy" ones to occur to the right of the verb without any special effect of foregrounding or backgrounding.</t>
+          <t>The Tensedness Universals of Adjective Encoding: A. If a language is tensed, it will have nouny adjectives.</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.736618131737829</v>
+        <v>-0.4006179472137477</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1483,21 +1483,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0798ka</t>
+          <t>0174ka</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>tensed &gt; N-like Pred Adj</t>
+          <t>Adp-N &amp; N-Num &gt; N-Gen</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>The Tensedness Universals of Adjective Encoding: A. If a language is tensed, it will have nouny adjectives.</t>
+          <t>If a language is prepositional, then if the numeral follows the noun, the genitive follows the noun.</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-0.47728847802789</v>
+        <v>0.7933595659083486</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1508,21 +1508,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0238bka</t>
+          <t>1216ka</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>rigid order &gt; N-Adj</t>
+          <t>N-Adp &gt; case (noun)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>If constituent order is rigid, all determined constituents precede their respective determining constituents; in particular, subjects precede their predicates, verbs their complements (objects, prepositional phrases), prepositions their complements (noun phrases), head nouns their attributive adjectives, relative clauses, and complements (prepositional phrases)</t>
+          <t>If there are (local) postpositions, then there will also be nominal case inflection (not necessarily including local cases, though).</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.332121080308733</v>
+        <v>0.5050527817023911</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.843975810665453</v>
+        <v>0.8368287735886084</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1558,21 +1558,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0174ka</t>
+          <t>1550ka</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Num &gt; N-Gen</t>
+          <t>V-initial &gt; N-Rel</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>If a language is prepositional, then if the numeral follows the noun, the genitive follows the noun.</t>
+          <t>In verb-initial languages the dominant order of relative clauses is always postnominal.</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.902521701428038</v>
+        <v>2.30409097369126</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1583,21 +1583,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1610ka</t>
+          <t>1372ka</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>verb-patient agreement &gt; V-initial | V-final</t>
+          <t>verb HAVE &gt; SVO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>In languages with verb agreement, patient verb agreement appears more frequently in verb-peripheral languages [i.e. verb-initial and verb-final languages] than in verb-medial languages.</t>
+          <t>A lexically distinct form of verb HAVE is generally missing in verb peripheral languages (i.e. SOV, VOS). That is, a verb HAVE is generally confined to SVO languages.</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.433337856540001</v>
+        <v>0.4891162799097322</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.279597397275955</v>
+        <v>0.2779576513293187</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1633,21 +1633,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0056ka</t>
+          <t>0238bka</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VSO &gt; N-Adj</t>
+          <t>rigid order &gt; N-Adj</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Universal 17. With overwhelmingly more than chance frequency, languages with dominant order VSO have the adjective after the noun.</t>
+          <t>If constituent order is rigid, all determined constituents precede their respective determining constituents; in particular, subjects precede their predicates, verbs their complements (objects, prepositional phrases), prepositions their complements (noun phrases), head nouns their attributive adjectives, relative clauses, and complements (prepositional phrases)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.78489603913086</v>
+        <v>0.3235147173074616</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1545ka</t>
+          <t>1610ka</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>V-initial &gt; N-Dem-Num-Adj</t>
+          <t>verb-patient agreement &gt; V-initial | V-final</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>In verb-initial languages, the demonstrative, numeral, and qualifying  adjective follow the common noun in that order or its mirror image (Adj + Num + Dem).</t>
+          <t>In languages with verb agreement, patient verb agreement appears more frequently in verb-peripheral languages [i.e. verb-initial and verb-final languages] than in verb-medial languages.</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-1.11661682029469</v>
+        <v>0.4733059117865276</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1683,23 +1683,98 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>1544ka</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>V-initial &gt; verbal case-marking</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>In verb-initial languages, verbal case marking is attested to a very significant degree. IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb. Standardized IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb.</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1.256095729197964</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>GPGLMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>1994bka</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>non-affixed Gen-N &gt; OV</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>-0.557202196284695</v>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D52" t="n">
+        <v>-0.5655262922540861</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GPGLMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0062aka</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rel-N &gt; Adj-N</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Universal 24. If the relative expression precedes the noun either as the only construction or as an alternate construction, either the language is postpositional, or the adjective precedes the noun or both.</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.5853835130788978</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>GPGLMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1545ka</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>V-initial &gt; N-Dem-Num-Adj</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>In verb-initial languages, the demonstrative, numeral, and qualifying  adjective follow the common noun in that order or its mirror image (Adj + Num + Dem).</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-1.17147815215299</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>GPGLMM</t>
         </is>

--- a/output/Table_B_Expansion.xlsx
+++ b/output/Table_B_Expansion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,21 +458,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0101ka</t>
+          <t>0001_or_2bka</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N-Gen &gt; N-Adj</t>
+          <t>N-Adp &gt; Gen-N</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>If the possessive adjective follows the noun, then the descriptive adjective follows the noun.</t>
+          <t>Universal 2. In languages with prepositions, the genitive almost always follows the governing noun, while in languages with postpositions it almost always precedes</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.263458887313696</v>
+        <v>1.214776970483311</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -483,21 +483,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1341ka</t>
+          <t>0088ka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>verbal reciprocal/reflexive &gt; verb agreement with subject</t>
+          <t>N-Dem &gt; N-Rel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>If a language has a verbal reciprocal/reflexive, it must have an overt AGR marker. Standardized IF there is a verbal reciprocal/reflexive, THEN there must be verb agreement at least with subject.</t>
+          <t>If a language has noun before demonstrative, then it has noun before relative clause.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.123052788661962</v>
+        <v>1.400039618483887</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -508,21 +508,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0917bka</t>
+          <t>0582ka</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OV &gt; Gen-N</t>
+          <t>inflection (noun) &gt; inflection (pronoun)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consistent OV languages are consistently left-branching (placing phrasal constituents before nonphrasal ones) while consistent VO languages are consistently right-branching.</t>
+          <t>If there is any inflection in nouns, there are also some inflections in pronouns.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.872708679895618</v>
+        <v>0.6197475983185543</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -533,21 +533,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0001_or_2bka</t>
+          <t>1427ka</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N-Adp &gt; Gen-N</t>
+          <t>no prefix &gt; infl local cases</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Universal 2. In languages with prepositions, the genitive almost always follows the governing noun, while in languages with postpositions it almost always precedes</t>
+          <t>If in a language there are no prefixes, then there will be inflectional (i.e. not prepositional) local cases.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.214776970483311</v>
+        <v>-0.9684874402709036</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -558,21 +558,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1591ka</t>
+          <t>1994aka</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>internal relative clause &gt; SOV</t>
+          <t>non-affixed Gen-N &gt; N-Adp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clear cases of internal relative clauses are present only in languages whose basic word order is SOV.</t>
+          <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.177530501362346</v>
+        <v>0.8919097611188793</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -583,21 +583,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0062bka</t>
+          <t>1827ka</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rel-N &gt; N-Adp</t>
+          <t>Rel-N | Adj-N &gt; Gen-N</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Universal 24. If the relative expression precedes the noun either as the only construction or as an alternate construction, either the language is postpositional, or the adjective precedes the noun or both.</t>
+          <t>If a language shows the order RelNoun or AdjNoun in its noun phrase, it is very likely to also show PossNoun, but not vice versa.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.318367109669455</v>
+        <v>0.8487445702647829</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -608,21 +608,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0088ka</t>
+          <t>1267aka</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N-Dem &gt; N-Rel</t>
+          <t>ergative &gt; VSO | SOV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>If a language has noun before demonstrative, then it has noun before relative clause.</t>
+          <t>Ergative systems are found only in SOV and VSO languages. SVO languages are never ergative.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.400039618483887</v>
+        <v>1.14618148201946</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -633,21 +633,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0577ka</t>
+          <t>0983ka</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>suppl noun &gt; suppl pron|verb</t>
+          <t>exceed comparative &gt; SVO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>If any inflectional category is expressed through suppletion in nouns, it is also expressed suppletively in pronouns or verbs.</t>
+          <t>If a language has an exceed comparative, then it is SVO.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.46868768103183</v>
+        <v>0.8002579058598616</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -658,21 +658,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0229ka</t>
+          <t>0507ka</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nominal number &gt; nominal case</t>
+          <t>(person)-number (verb) &gt; tense-mood (verb)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>If nominals inflect for number, they also inflect for case.</t>
+          <t>If the verb has categories of person-number or if it has categories of gender, it always has tense-mood categories.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6648923245892728</v>
+        <v>0.9402568206468179</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -683,21 +683,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0582ka</t>
+          <t>0147ka</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>inflection (noun) &gt; inflection (pronoun)</t>
+          <t>V-like Attr Adj &gt; SVO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>If there is any inflection in nouns, there are also some inflections in pronouns.</t>
+          <t>If attributive adjectives have the form of relative clauses, there is a positive correlation with SVO.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6197475983185543</v>
+        <v>-0.5407045909718766</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -708,21 +708,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1667aka</t>
+          <t>0008ka</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S-Comp &gt; SOV</t>
+          <t>SOV|OSV &gt; case</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>There is a tendency for conjunctions (including comlementizers) to occur in clause-final position in SOV languages and in clause-initial position in VSO languages.</t>
+          <t>Universal 41. If in a language the verb follows both the nominal subject and nominal object as the dominant order, the language almost always has a case system.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.343421666206671</v>
+        <v>0.8683754606800662</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -733,21 +733,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0091ka</t>
+          <t>0964bka</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adp-N &amp; N-Adj &gt; N-Rel</t>
+          <t>OV &gt; N-Art</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IF a language has Prep word order, then if the adjective follows the noun, the relative clause follows the noun.</t>
+          <t>VO languages exhibit a statistically greater tendency to place articles before the noun than OV languages do. To the opposite, the tendency to place the noun before the articles is higher among OV languages than it is among VO languages.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.812095823486219</v>
+        <v>0.7995804208801867</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -758,21 +758,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1427ka</t>
+          <t>0070ka</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no prefix &gt; infl local cases</t>
+          <t>Adp-N &amp; no SVO &amp; N-Adj &gt; N-Gen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>If in a language there are no prefixes, then there will be inflectional (i.e. not prepositional) local cases.</t>
+          <t>If a language has prepositions and any verb position other than SVO, then if the adjectives follows the noun, the genitive follows the noun.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.9684874402709036</v>
+        <v>0.9936874289930697</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1994dka</t>
+          <t>1434ka</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>non-affixed Gen-N &gt; Adj-N</t>
+          <t>many tenses &gt; no aspect</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
+          <t>A large number of tense oppositions correlates with the absence of aspect differentiation.</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.194464966759849</v>
+        <v>0.473181485800218</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0178ka</t>
+          <t>0116ka</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N-Adp &amp; Num-N &gt; Gen-N</t>
+          <t>case &gt; number</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>If a language has Postp word order, then if the numeral precedes the noun, the genitive precedes the noun.</t>
+          <t>number is, as has been seen, closer to the stem and generally present when case is present, while the opposite relation holds far more rarely.</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.110359375235017</v>
+        <v>0.3399723047312557</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -833,21 +833,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1994aka</t>
+          <t>0798ka</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>non-affixed Gen-N &gt; N-Adp</t>
+          <t>tensed &gt; N-like Pred Adj</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
+          <t>The Tensedness Universals of Adjective Encoding: A. If a language is tensed, it will have nouny adjectives.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.8919097611188793</v>
+        <v>-0.4006179472137477</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -858,21 +858,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0071ka</t>
+          <t>0174ka</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>N-Adp &amp; Adj-N &gt; Gen-N</t>
+          <t>Adp-N &amp; N-Num &gt; N-Gen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>If a language has Postp word order, and if the adjective precedes the noun, then the genitive precedes the noun.</t>
+          <t>If a language is prepositional, then if the numeral follows the noun, the genitive follows the noun.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.479624613181985</v>
+        <v>0.7933595659083486</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -883,21 +883,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0493bka</t>
+          <t>1216ka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sent-Q &gt; N-Adp</t>
+          <t>N-Adp &gt; case (noun)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Universal 9. With well more than chance frequency, when question particles or affixes are specified in position by reference to the sentence as a whole, if initial, such elements are found in prepositional languages, and, if final, in postpositional.</t>
+          <t>If there are (local) postpositions, then there will also be nominal case inflection (not necessarily including local cases, though).</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.6554210903288318</v>
+        <v>0.5050527817023911</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1827ka</t>
+          <t>0095bka</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rel-N | Adj-N &gt; Gen-N</t>
+          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; Num-N</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>If a language shows the order RelNoun or AdjNoun in its noun phrase, it is very likely to also show PossNoun, but not vice versa.</t>
+          <t>IF there are postpositions, THEN (IF adjectives precede nouns or relatives precede nouns, THEN demonstratives preced nouns and numerals precede nouns) and (IF demonstratives precede nouns or numerals precede nouns, THEN genitives precede nouns).</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8487445702647829</v>
+        <v>0.8368287735886084</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0110ka</t>
+          <t>1372ka</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>N-Rel &gt; N-Adj</t>
+          <t>verb HAVE &gt; SVO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>There is a clear tendency for Rel N languages to be Adj N and for N Rel languages to be N Adj.</t>
+          <t>A lexically distinct form of verb HAVE is generally missing in verb peripheral languages (i.e. SOV, VOS). That is, a verb HAVE is generally confined to SVO languages.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8680778033647435</v>
+        <v>0.4891162799097322</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -958,21 +958,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1267aka</t>
+          <t>0572ka</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ergative &gt; VSO | SOV</t>
+          <t>obli (in)Def marking &gt; obli PL marking (noun)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ergative systems are found only in SOV and VSO languages. SVO languages are never ergative.</t>
+          <t>If a language has obligatory marking of (in)definiteness, then it has obligatory marking of nominal plurality (but not vice versa).</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.14618148201946</v>
+        <v>0.2779576513293187</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -983,21 +983,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0982ka</t>
+          <t>0238bka</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>locative comparative &gt; SOV | VSO</t>
+          <t>rigid order &gt; N-Adj</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>If a language has a locative comparative, then it is either SOV or VSO.</t>
+          <t>If constituent order is rigid, all determined constituents precede their respective determining constituents; in particular, subjects precede their predicates, verbs their complements (objects, prepositional phrases), prepositions their complements (noun phrases), head nouns their attributive adjectives, relative clauses, and complements (prepositional phrases)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7824118196564633</v>
+        <v>0.3235147173074616</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1008,21 +1008,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0983ka</t>
+          <t>1610ka</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>exceed comparative &gt; SVO</t>
+          <t>verb-patient agreement &gt; V-initial | V-final</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>If a language has an exceed comparative, then it is SVO.</t>
+          <t>In languages with verb agreement, patient verb agreement appears more frequently in verb-peripheral languages [i.e. verb-initial and verb-final languages] than in verb-medial languages.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.8002579058598616</v>
+        <v>0.4733059117865276</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0493aka</t>
+          <t>1544ka</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q-Sent &gt; Adp-N</t>
+          <t>V-initial &gt; verbal case-marking</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Universal 9. With well more than chance frequency, when question particles or affixes are specified in position by reference to the sentence as a whole, if initial, such elements are found in prepositional languages, and, if final, in postpositional.</t>
+          <t>In verb-initial languages, verbal case marking is attested to a very significant degree. IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb. Standardized IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8773918990590241</v>
+        <v>1.256095729197964</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1058,723 +1058,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1431nka</t>
+          <t>0062aka</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>more case &gt; less tense</t>
+          <t>Rel-N &gt; Adj-N</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>The more developed a case system is, the less is its system of verbal tenses.</t>
+          <t>Universal 24. If the relative expression precedes the noun either as the only construction or as an alternate construction, either the language is postpositional, or the adjective precedes the noun or both.</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.7330741943451813</v>
+        <v>0.5853835130788978</v>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>0507ka</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>(person)-number (verb) &gt; tense-mood (verb)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>If the verb has categories of person-number or if it has categories of gender, it always has tense-mood categories.</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0.9402568206468179</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>0065_or_66ka</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SOV &amp; Adj-N &gt; Gen-N</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>If a language has SOV word order, then if the adjective precedes the noun, the genitive precedes the noun. If a language has dominant SOV order and the genitive follows the governing noun, then the adjective likewise follows the noun.</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1.267659628830224</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>0147ka</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>V-like Attr Adj &gt; SVO</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>If attributive adjectives have the form of relative clauses, there is a positive correlation with SVO.</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>-0.5407045909718766</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1612cka</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>SOV &amp; N-Num &gt; N-Num agr</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>In SOV languages, when the expected order of Modifier-Noun does not occur,  agreement [between noun and modifier] tends to appear.</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>-4.266092981394785</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>0008ka</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SOV|OSV &gt; case</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Universal 41. If in a language the verb follows both the nominal subject and nominal object as the dominant order, the language almost always has a case system.</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0.8683754606800662</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>0245aka</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>free order &gt; inflection nouns</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>If constituent order is free without limits, then nominal words are inflected, but not vice versa; if constituent order is rigid without inversions, then there is no nominal inflection, but again not vice versa.</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0.4236947200639888</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>0231bka</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>free order | case &gt; gradation adj inflect</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>If constituent order is rigid (or if there is no case inflection), then the gradation of adjectives is expressed by function words; if constituent order is flexible (or if there is case inflection), then the gradation of adjectives is expressed inflectionally.</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0.7408322774174536</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>0964bka</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>OV &gt; N-Art</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>VO languages exhibit a statistically greater tendency to place articles before the noun than OV languages do. To the opposite, the tendency to place the noun before the articles is higher among OV languages than it is among VO languages.</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0.7995804208801867</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1027bka</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no morph tense -&gt; no case|VO</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>There are correlations between following parameters: VO word order, Non-tensedness, Non-casedness, WITH-Construction, Non-Absolute Converb. Standardized IF VO, THEN Non-tensedness, Non-casedness, WITH-Construction, and Non-Absolute Converb. IF Non-tensedness, THEN VO, Non-casedness, WITH-Construction, and Non-Absolute Converb. IF Non-casedness, THEN VO, Non-tensedness, WITH-Construction, and Non-Absolute Converb. IF AND-construction, THEN VO, Non-tensedness, Non-casedness, and Non-Absolute Converb. IF Non-Absolute Converb, THEN VO, Non-tensedness, Non-casedness, and WITH-Construction.</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0.6468513608332771</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>0070ka</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Adp-N &amp; no SVO &amp; N-Adj &gt; N-Gen</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>If a language has prepositions and any verb position other than SVO, then if the adjectives follows the noun, the genitive follows the noun.</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0.9936874289930697</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1592ka</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>internal relative clause &gt; left-branching NP structure</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>The restriction of internally headed relative clauses to OV languages implies that these relative clauses are found in languages having left-branching rather than (in addition to) right-branching NP structure.</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0.6092661184715494</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1434ka</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>many tenses &gt; no aspect</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>A large number of tense oppositions correlates with the absence of aspect differentiation.</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0.473181485800218</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>0116ka</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>case &gt; number</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>number is, as has been seen, closer to the stem and generally present when case is present, while the opposite relation holds far more rarely.</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0.3399723047312557</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>0822ka</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>correlative Rel &gt; V-final;</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Correlatives are limited to verb-final languages, and in fact, are largely limited to "loose" verb-final ones, namely which permit some NPs, especially "heavy" ones to occur to the right of the verb without any special effect of foregrounding or backgrounding.</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>0.7531105468410542</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>0228ka</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>nominal case &gt; verbal inflection</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>If nouns inflect for case, then verbs inflect for some inflectional category.</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1.492674779222098</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>0798ka</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>tensed &gt; N-like Pred Adj</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>The Tensedness Universals of Adjective Encoding: A. If a language is tensed, it will have nouny adjectives.</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>-0.4006179472137477</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>0174ka</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Adp-N &amp; N-Num &gt; N-Gen</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>If a language is prepositional, then if the numeral follows the noun, the genitive follows the noun.</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0.7933595659083486</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1216ka</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>N-Adp &gt; case (noun)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>If there are (local) postpositions, then there will also be nominal case inflection (not necessarily including local cases, though).</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0.5050527817023911</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>0095bka</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; Num-N</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>IF there are postpositions, THEN (IF adjectives precede nouns or relatives precede nouns, THEN demonstratives preced nouns and numerals precede nouns) and (IF demonstratives precede nouns or numerals precede nouns, THEN genitives precede nouns).</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0.8368287735886084</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1550ka</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>V-initial &gt; N-Rel</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>In verb-initial languages the dominant order of relative clauses is always postnominal.</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2.30409097369126</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>1372ka</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>verb HAVE &gt; SVO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>A lexically distinct form of verb HAVE is generally missing in verb peripheral languages (i.e. SOV, VOS). That is, a verb HAVE is generally confined to SVO languages.</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0.4891162799097322</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>0572ka</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>obli (in)Def marking &gt; obli PL marking (noun)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>If a language has obligatory marking of (in)definiteness, then it has obligatory marking of nominal plurality (but not vice versa).</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0.2779576513293187</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>0238bka</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>rigid order &gt; N-Adj</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>If constituent order is rigid, all determined constituents precede their respective determining constituents; in particular, subjects precede their predicates, verbs their complements (objects, prepositional phrases), prepositions their complements (noun phrases), head nouns their attributive adjectives, relative clauses, and complements (prepositional phrases)</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0.3235147173074616</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1610ka</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>verb-patient agreement &gt; V-initial | V-final</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>In languages with verb agreement, patient verb agreement appears more frequently in verb-peripheral languages [i.e. verb-initial and verb-final languages] than in verb-medial languages.</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>0.4733059117865276</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1544ka</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>V-initial &gt; verbal case-marking</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>In verb-initial languages, verbal case marking is attested to a very significant degree. IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb. Standardized IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb.</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>1.256095729197964</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>1994bka</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>non-affixed Gen-N &gt; OV</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>-0.5655262922540861</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>0062aka</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Rel-N &gt; Adj-N</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Universal 24. If the relative expression precedes the noun either as the only construction or as an alternate construction, either the language is postpositional, or the adjective precedes the noun or both.</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0.5853835130788978</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1545ka</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>V-initial &gt; N-Dem-Num-Adj</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>In verb-initial languages, the demonstrative, numeral, and qualifying  adjective follow the common noun in that order or its mirror image (Adj + Num + Dem).</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>-1.17147815215299</v>
-      </c>
-      <c r="E54" t="inlineStr">
         <is>
           <t>GPGLMM</t>
         </is>

--- a/output/Table_B_Expansion.xlsx
+++ b/output/Table_B_Expansion.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,21 +458,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0001_or_2bka</t>
+          <t>0121ka</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N-Adp &gt; Gen-N</t>
+          <t>Adp-N &amp; N-Num &gt; N-Rel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Universal 2. In languages with prepositions, the genitive almost always follows the governing noun, while in languages with postpositions it almost always precedes</t>
+          <t>If a language is prepositional, then if the numeral follows the noun, the relative clause follows the noun.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.214776970483311</v>
+        <v>2.268331062668192</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -483,21 +483,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0088ka</t>
+          <t>0001_or_2bka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N-Dem &gt; N-Rel</t>
+          <t>N-Adp &gt; Gen-N</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>If a language has noun before demonstrative, then it has noun before relative clause.</t>
+          <t>Universal 2. In languages with prepositions, the genitive almost always follows the governing noun, while in languages with postpositions it almost always precedes</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.400039618483887</v>
+        <v>1.171566066034621</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -508,21 +508,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0582ka</t>
+          <t>0230dka</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>inflection (noun) &gt; inflection (pronoun)</t>
+          <t>free order &gt; case</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>If there is any inflection in nouns, there are also some inflections in pronouns.</t>
+          <t>IF constituent order is rigid, THEN cases are absent, and vice versa; ; If cases are absent, THEN the use of prepositions is extensive, and vice versa;; IF order is rigid, THEN the use of prepositions is extensive, and vice versa. : IF constituent order is flexible, THEN cases are present, and vice versa; ; IF cases are present, THEN the use of prepositions is sparse, and vice versa; ; IF order is flexible, THEN the use of prepositions is sparse, and vice versa.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6197475983185543</v>
+        <v>-0.7586799760782996</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -533,21 +533,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1427ka</t>
+          <t>0230aka</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no prefix &gt; infl local cases</t>
+          <t>rigid order &gt; no case</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>If in a language there are no prefixes, then there will be inflectional (i.e. not prepositional) local cases.</t>
+          <t>IF constituent order is rigid, THEN cases are absent, and vice versa; ; If cases are absent, THEN the use of prepositions is extensive, and vice versa;; IF order is rigid, THEN the use of prepositions is extensive, and vice versa. : IF constituent order is flexible, THEN cases are present, and vice versa; ; IF cases are present, THEN the use of prepositions is sparse, and vice versa; ; IF order is flexible, THEN the use of prepositions is sparse, and vice versa.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.9684874402709036</v>
+        <v>-0.7702833964444548</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -558,21 +558,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1994aka</t>
+          <t>0088ka</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>non-affixed Gen-N &gt; N-Adp</t>
+          <t>N-Dem &gt; N-Rel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
+          <t>If a language has noun before demonstrative, then it has noun before relative clause.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8919097611188793</v>
+        <v>1.318753268193772</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -583,21 +583,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1827ka</t>
+          <t>1994aka</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rel-N | Adj-N &gt; Gen-N</t>
+          <t>non-affixed Gen-N &gt; N-Adp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>If a language shows the order RelNoun or AdjNoun in its noun phrase, it is very likely to also show PossNoun, but not vice versa.</t>
+          <t>Hier nun war es möglich, scheinbar sich sogar auf einen einzigen Gegenstand zu beschränken, nämlich DIE STELLUNG DES AFFIXLOSEN GENITIVS in bezug auf den Nominativ, den er näher bestimmt. Scheinbar, denn in Wirklichkeit schließen an diesen Gegenstand in psychologischer Notwendigkeit eine ganze Reihe von grundlegenden Elementen der Satzbildung sich an und werden durch ihn in weitgehendem Maße bestimmt und beeinflußt. Es steht mit der Genitivstellung in engstem Zusammenhang die Bildung und Stellung des vom Personalpronomen abgeleiteten POSSESSIVS. Bei dessen tieferer Behandlung stößt man auch auf das Problem der Form und Stellung des PERSONALPRONOMENS ALS SUBJEKT DER SÄTZE, insbesondere der Verbalsätze.  Nachdem in diesen beiden wichtigen Punkten die weitgehende Bedeutung der Genitivstellung zutage getreten ist, wirft  sich bald auch die Frage auf, ob nicht auch bei einem anderen wichtigen Kasus, dem AKKUSATIV, seine Stellung zu dem Verb, von dem er abhängt, in enger Beziehung zu der des Genitiv stehe oder gar von ihr maßgebend bestimmt werde. Die gleiche Frage drängt sich dann auch auf in bezug auf die Stellung des ADJEKTIVS zu dem Substantiv, das es näher bestimmt. Standardized IF the attributive noun (genitive, esp. when morphologically unmarked) precedes the head noun, THEN (i) nominal affixes (for case, number, gender/class) and adpositions are postposed (suffixes, postpositions), (ii) pronominal possessives precede the head noun, (iii) attributive adjectives precede the head noun, (iv) verbal affixes (person, number) and pronouns (for subject) precede the verb, (v) direct objects (accusative, esp. when morphologically unmarked) precede the verb.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8487445702647829</v>
+        <v>0.9828849533820356</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -608,21 +608,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1267aka</t>
+          <t>1427ka</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ergative &gt; VSO | SOV</t>
+          <t>no prefix &gt; infl local cases</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ergative systems are found only in SOV and VSO languages. SVO languages are never ergative.</t>
+          <t>If in a language there are no prefixes, then there will be inflectional (i.e. not prepositional) local cases.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.14618148201946</v>
+        <v>-0.9328968996204233</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -633,21 +633,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0983ka</t>
+          <t>1267aka</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>exceed comparative &gt; SVO</t>
+          <t>ergative &gt; VSO | SOV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>If a language has an exceed comparative, then it is SVO.</t>
+          <t>Ergative systems are found only in SOV and VSO languages. SVO languages are never ergative.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8002579058598616</v>
+        <v>1.157786847514599</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -658,21 +658,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0507ka</t>
+          <t>1544ka</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(person)-number (verb) &gt; tense-mood (verb)</t>
+          <t>V-initial &gt; verbal case-marking</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>If the verb has categories of person-number or if it has categories of gender, it always has tense-mood categories.</t>
+          <t>In verb-initial languages, verbal case marking is attested to a very significant degree. IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb. Standardized IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9402568206468179</v>
+        <v>1.666261773045432</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -683,21 +683,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0147ka</t>
+          <t>0116ka</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V-like Attr Adj &gt; SVO</t>
+          <t>case &gt; number</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>If attributive adjectives have the form of relative clauses, there is a positive correlation with SVO.</t>
+          <t>number is, as has been seen, closer to the stem and generally present when case is present, while the opposite relation holds far more rarely.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.5407045909718766</v>
+        <v>0.6816420539097781</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8683754606800662</v>
+        <v>0.8942674111664515</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -733,21 +733,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0964bka</t>
+          <t>0174ka</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OV &gt; N-Art</t>
+          <t>Adp-N &amp; N-Num &gt; N-Gen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VO languages exhibit a statistically greater tendency to place articles before the noun than OV languages do. To the opposite, the tendency to place the noun before the articles is higher among OV languages than it is among VO languages.</t>
+          <t>If a language is prepositional, then if the numeral follows the noun, the genitive follows the noun.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7995804208801867</v>
+        <v>1.248415666157829</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -758,21 +758,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0070ka</t>
+          <t>0582ka</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adp-N &amp; no SVO &amp; N-Adj &gt; N-Gen</t>
+          <t>inflection (noun) &gt; inflection (pronoun)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>If a language has prepositions and any verb position other than SVO, then if the adjectives follows the noun, the genitive follows the noun.</t>
+          <t>If there is any inflection in nouns, there are also some inflections in pronouns.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.9936874289930697</v>
+        <v>0.6325078622338849</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1434ka</t>
+          <t>0095bka</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>many tenses &gt; no aspect</t>
+          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; Num-N</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A large number of tense oppositions correlates with the absence of aspect differentiation.</t>
+          <t>IF there are postpositions, THEN (IF adjectives precede nouns or relatives precede nouns, THEN demonstratives preced nouns and numerals precede nouns) and (IF demonstratives precede nouns or numerals precede nouns, THEN genitives precede nouns).</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.473181485800218</v>
+        <v>0.8955147914257173</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0116ka</t>
+          <t>0507ka</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>case &gt; number</t>
+          <t>(person)-number (verb) &gt; tense-mood (verb)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>number is, as has been seen, closer to the stem and generally present when case is present, while the opposite relation holds far more rarely.</t>
+          <t>If the verb has categories of person-number or if it has categories of gender, it always has tense-mood categories.</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.3399723047312557</v>
+        <v>0.8735626585316155</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -833,248 +833,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0798ka</t>
+          <t>1612dka</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tensed &gt; N-like Pred Adj</t>
+          <t>SOV &amp; N-Dem &gt; N-Dem agr</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The Tensedness Universals of Adjective Encoding: A. If a language is tensed, it will have nouny adjectives.</t>
+          <t>In SOV languages, when the expected order of Modifier-Noun does not occur,  agreement [between noun and modifier] tends to appear.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.4006179472137477</v>
+        <v>-1.467422417098351</v>
       </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>0174ka</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Adp-N &amp; N-Num &gt; N-Gen</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>If a language is prepositional, then if the numeral follows the noun, the genitive follows the noun.</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.7933595659083486</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>1216ka</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>N-Adp &gt; case (noun)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>If there are (local) postpositions, then there will also be nominal case inflection (not necessarily including local cases, though).</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.5050527817023911</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>0095bka</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>N-Adp &amp; (Adj-N | Rel-N) &gt; Num-N</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>IF there are postpositions, THEN (IF adjectives precede nouns or relatives precede nouns, THEN demonstratives preced nouns and numerals precede nouns) and (IF demonstratives precede nouns or numerals precede nouns, THEN genitives precede nouns).</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0.8368287735886084</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1372ka</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>verb HAVE &gt; SVO</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>A lexically distinct form of verb HAVE is generally missing in verb peripheral languages (i.e. SOV, VOS). That is, a verb HAVE is generally confined to SVO languages.</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0.4891162799097322</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>0572ka</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>obli (in)Def marking &gt; obli PL marking (noun)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>If a language has obligatory marking of (in)definiteness, then it has obligatory marking of nominal plurality (but not vice versa).</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0.2779576513293187</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>0238bka</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>rigid order &gt; N-Adj</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>If constituent order is rigid, all determined constituents precede their respective determining constituents; in particular, subjects precede their predicates, verbs their complements (objects, prepositional phrases), prepositions their complements (noun phrases), head nouns their attributive adjectives, relative clauses, and complements (prepositional phrases)</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0.3235147173074616</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1610ka</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>verb-patient agreement &gt; V-initial | V-final</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>In languages with verb agreement, patient verb agreement appears more frequently in verb-peripheral languages [i.e. verb-initial and verb-final languages] than in verb-medial languages.</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0.4733059117865276</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1544ka</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>V-initial &gt; verbal case-marking</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>In verb-initial languages, verbal case marking is attested to a very significant degree. IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb. Standardized IF word order is verb-initial, THEN there is relational marking (agreement, applicative, etc.) associated with the verb.</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1.256095729197964</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>GPGLMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>0062aka</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Rel-N &gt; Adj-N</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Universal 24. If the relative expression precedes the noun either as the only construction or as an alternate construction, either the language is postpositional, or the adjective precedes the noun or both.</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0.5853835130788978</v>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>GPGLMM</t>
         </is>
